--- a/manufacturing_forms/019_production_site_size_survey--manufacturing_forms.xlsx
+++ b/manufacturing_forms/019_production_site_size_survey--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>production_capacity</t>
+          <t>production_capacity_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Production Capacity</t>
+          <t>Production Capacity 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>production_capacity_unit</t>
+          <t>production_capacity_unit_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Production Capacity Unit</t>
+          <t>Production Capacity Unit 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>production_capacity_factor</t>
+          <t>production_capacity_factor_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Production Capacity Factor</t>
+          <t>Production Capacity Factor 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>production_area</t>
+          <t>production_area_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Production Area</t>
+          <t>Production Area 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>production_capacity_unit_choices</t>
+          <t>production_capacity_unit_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>production_capacity_unit_choices</t>
+          <t>production_capacity_unit_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>production_capacity_unit_choices</t>
+          <t>production_capacity_unit_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
